--- a/CEO Review.xlsx
+++ b/CEO Review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peoplestronghrservices-my.sharepoint.com/personal/baljeet_singh_taggd_in/Documents/Desktop/Clude Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1431" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A4DB35B-38AD-4A36-962A-C86CF23AEA78}"/>
+  <xr:revisionPtr revIDLastSave="1435" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF9D860E-2181-4CFD-851D-876107001E50}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
   </bookViews>
@@ -11245,9 +11245,7 @@
       <c r="E60" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="G60" s="23">
-        <v>217</v>
-      </c>
+      <c r="G60" s="23"/>
       <c r="H60" s="24">
         <v>0</v>
       </c>
@@ -11275,7 +11273,7 @@
       </c>
       <c r="AY60" s="17">
         <f t="shared" si="5"/>
-        <v>2531</v>
+        <v>2314</v>
       </c>
       <c r="AZ60" s="17">
         <f t="shared" si="5"/>

--- a/CEO Review.xlsx
+++ b/CEO Review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peoplestronghrservices-my.sharepoint.com/personal/baljeet_singh_taggd_in/Documents/Desktop/Clude Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1435" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF9D860E-2181-4CFD-851D-876107001E50}"/>
+  <xr:revisionPtr revIDLastSave="1436" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C5B551E-EC47-4E75-A973-DF5A246AF66D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
   </bookViews>
@@ -11245,7 +11245,9 @@
       <c r="E60" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="G60" s="23"/>
+      <c r="G60" s="23">
+        <v>217</v>
+      </c>
       <c r="H60" s="24">
         <v>0</v>
       </c>
@@ -11273,7 +11275,7 @@
       </c>
       <c r="AY60" s="17">
         <f t="shared" si="5"/>
-        <v>2314</v>
+        <v>2531</v>
       </c>
       <c r="AZ60" s="17">
         <f t="shared" si="5"/>

--- a/CEO Review.xlsx
+++ b/CEO Review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peoplestronghrservices-my.sharepoint.com/personal/baljeet_singh_taggd_in/Documents/Desktop/Clude Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1436" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C5B551E-EC47-4E75-A973-DF5A246AF66D}"/>
+  <xr:revisionPtr revIDLastSave="1437" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F8AC8EA-1D49-4A46-9C35-B893FDC60E46}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
   </bookViews>
@@ -11245,9 +11245,7 @@
       <c r="E60" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="G60" s="23">
-        <v>217</v>
-      </c>
+      <c r="G60" s="23"/>
       <c r="H60" s="24">
         <v>0</v>
       </c>
@@ -11275,7 +11273,7 @@
       </c>
       <c r="AY60" s="17">
         <f t="shared" si="5"/>
-        <v>2531</v>
+        <v>2314</v>
       </c>
       <c r="AZ60" s="17">
         <f t="shared" si="5"/>

--- a/CEO Review.xlsx
+++ b/CEO Review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peoplestronghrservices-my.sharepoint.com/personal/baljeet_singh_taggd_in/Documents/Desktop/Clude Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1437" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F8AC8EA-1D49-4A46-9C35-B893FDC60E46}"/>
+  <xr:revisionPtr revIDLastSave="1438" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{865F7A44-37C2-4282-A841-1D6D98B3DEA0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
   </bookViews>
@@ -11245,7 +11245,9 @@
       <c r="E60" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="G60" s="23"/>
+      <c r="G60" s="23">
+        <v>217</v>
+      </c>
       <c r="H60" s="24">
         <v>0</v>
       </c>
@@ -11273,7 +11275,7 @@
       </c>
       <c r="AY60" s="17">
         <f t="shared" si="5"/>
-        <v>2314</v>
+        <v>2531</v>
       </c>
       <c r="AZ60" s="17">
         <f t="shared" si="5"/>

--- a/CEO Review.xlsx
+++ b/CEO Review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peoplestronghrservices-my.sharepoint.com/personal/baljeet_singh_taggd_in/Documents/Desktop/Clude Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1438" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{865F7A44-37C2-4282-A841-1D6D98B3DEA0}"/>
+  <xr:revisionPtr revIDLastSave="1455" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2B404CA-36CB-4987-9A65-7DDA74EBADA9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$BZ$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$BZ$60</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1318,7 +1318,7 @@
         <v>107620.37733721343</v>
       </c>
       <c r="L3" s="17">
-        <v>172</v>
+        <v>57.333333333333336</v>
       </c>
       <c r="M3" s="17"/>
       <c r="N3" s="6"/>
@@ -1344,7 +1344,7 @@
         <v>118382.41507093479</v>
       </c>
       <c r="W3" s="17">
-        <v>172</v>
+        <v>57.333333333333336</v>
       </c>
       <c r="X3" s="17"/>
       <c r="Y3" s="17"/>
@@ -1369,7 +1369,7 @@
         <v>118382.41507093479</v>
       </c>
       <c r="AH3" s="17">
-        <v>172</v>
+        <v>57.333333333333336</v>
       </c>
       <c r="AI3" s="17"/>
       <c r="AJ3" s="17"/>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="AS3" s="17">
         <f>AH3</f>
-        <v>172</v>
+        <v>57.333333333333336</v>
       </c>
       <c r="AT3" s="17"/>
       <c r="AU3" s="17"/>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="BD3" s="3">
         <f t="shared" ref="BD3:BD34" si="1">AVERAGE(L3,W3,AH3,AS3)</f>
-        <v>172</v>
+        <v>57.333333333333336</v>
       </c>
       <c r="BE3" s="3"/>
       <c r="BF3" s="3"/>
@@ -1495,7 +1495,7 @@
         <v>173405.52273207638</v>
       </c>
       <c r="L4" s="17">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M4" s="17"/>
       <c r="N4" s="6"/>
@@ -1521,7 +1521,7 @@
         <v>190746.07500528404</v>
       </c>
       <c r="W4" s="17">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="X4" s="17"/>
       <c r="Y4" s="17"/>
@@ -1545,7 +1545,7 @@
         <v>190746.07500528404</v>
       </c>
       <c r="AH4" s="17">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AI4" s="17"/>
       <c r="AJ4" s="17"/>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="AS4" s="17">
         <f t="shared" ref="AS4:AS59" si="4">AH4</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AT4" s="17"/>
       <c r="AU4" s="17"/>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="BD4" s="3">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BE4" s="3"/>
       <c r="BF4" s="3"/>
@@ -1670,7 +1670,7 @@
         <v>100967.52669613245</v>
       </c>
       <c r="L5" s="17">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M5" s="17"/>
       <c r="N5" s="6"/>
@@ -1696,7 +1696,7 @@
         <v>111064.27936574571</v>
       </c>
       <c r="W5" s="17">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="X5" s="17"/>
       <c r="Y5" s="17"/>
@@ -1720,7 +1720,7 @@
         <v>111064.27936574571</v>
       </c>
       <c r="AH5" s="17">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AI5" s="17"/>
       <c r="AJ5" s="17"/>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="AS5" s="17">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AT5" s="17"/>
       <c r="AU5" s="17"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="BD5" s="3">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="BE5" s="3"/>
       <c r="BF5" s="3"/>
@@ -1847,7 +1847,7 @@
         <v>110580.54850844618</v>
       </c>
       <c r="L6" s="17">
-        <v>47</v>
+        <v>15.666666666666666</v>
       </c>
       <c r="M6" s="17"/>
       <c r="N6" s="6"/>
@@ -1873,7 +1873,7 @@
         <v>121638.60335929081</v>
       </c>
       <c r="W6" s="17">
-        <v>47</v>
+        <v>15.666666666666666</v>
       </c>
       <c r="X6" s="17"/>
       <c r="Y6" s="17"/>
@@ -1897,7 +1897,7 @@
         <v>121638.60335929081</v>
       </c>
       <c r="AH6" s="17">
-        <v>47</v>
+        <v>15.666666666666666</v>
       </c>
       <c r="AI6" s="17"/>
       <c r="AJ6" s="17"/>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AS6" s="17">
         <f t="shared" si="4"/>
-        <v>47</v>
+        <v>15.666666666666666</v>
       </c>
       <c r="AT6" s="17"/>
       <c r="AU6" s="17"/>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="BD6" s="3">
         <f t="shared" si="1"/>
-        <v>47</v>
+        <v>15.666666666666666</v>
       </c>
       <c r="BE6" s="3"/>
       <c r="BF6" s="3"/>
@@ -2029,7 +2029,7 @@
         <v>101311.4009425254</v>
       </c>
       <c r="L7" s="17">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="M7" s="17"/>
       <c r="N7" s="6"/>
@@ -2055,7 +2055,7 @@
         <v>111442.54103677796</v>
       </c>
       <c r="W7" s="17">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="X7" s="17"/>
       <c r="Y7" s="17"/>
@@ -2079,7 +2079,7 @@
         <v>111442.54103677796</v>
       </c>
       <c r="AH7" s="17">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AI7" s="17"/>
       <c r="AJ7" s="17"/>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AS7" s="17">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AT7" s="17"/>
       <c r="AU7" s="17"/>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="BD7" s="3">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="BE7" s="3"/>
       <c r="BF7" s="3"/>
@@ -2207,7 +2207,7 @@
         <v>101000</v>
       </c>
       <c r="L8" s="17">
-        <v>24.5</v>
+        <v>8.1666666666666661</v>
       </c>
       <c r="M8" s="17"/>
       <c r="N8" s="6"/>
@@ -2233,7 +2233,7 @@
         <v>111100.00000000001</v>
       </c>
       <c r="W8" s="17">
-        <v>24.5</v>
+        <v>8.1666666666666661</v>
       </c>
       <c r="X8" s="17"/>
       <c r="Y8" s="17"/>
@@ -2257,7 +2257,7 @@
         <v>111100.00000000001</v>
       </c>
       <c r="AH8" s="17">
-        <v>24.5</v>
+        <v>8.1666666666666661</v>
       </c>
       <c r="AI8" s="17"/>
       <c r="AJ8" s="17"/>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="AS8" s="17">
         <f t="shared" si="4"/>
-        <v>24.5</v>
+        <v>8.1666666666666661</v>
       </c>
       <c r="AT8" s="17"/>
       <c r="AU8" s="17"/>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="BD8" s="3">
         <f t="shared" si="1"/>
-        <v>24.5</v>
+        <v>8.1666666666666661</v>
       </c>
       <c r="BE8" s="3"/>
       <c r="BF8" s="3"/>
@@ -2382,7 +2382,7 @@
         <v>80180.641691213954</v>
       </c>
       <c r="L9" s="17">
-        <v>32</v>
+        <v>10.666666666666666</v>
       </c>
       <c r="M9" s="17"/>
       <c r="N9" s="6"/>
@@ -2408,7 +2408,7 @@
         <v>88198.705860335351</v>
       </c>
       <c r="W9" s="17">
-        <v>32</v>
+        <v>10.666666666666666</v>
       </c>
       <c r="X9" s="17"/>
       <c r="Y9" s="17"/>
@@ -2432,7 +2432,7 @@
         <v>88198.705860335351</v>
       </c>
       <c r="AH9" s="17">
-        <v>32</v>
+        <v>10.666666666666666</v>
       </c>
       <c r="AI9" s="17"/>
       <c r="AJ9" s="17"/>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AS9" s="17">
         <f t="shared" si="4"/>
-        <v>32</v>
+        <v>10.666666666666666</v>
       </c>
       <c r="AT9" s="17"/>
       <c r="AU9" s="17"/>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="BD9" s="3">
         <f t="shared" si="1"/>
-        <v>32</v>
+        <v>10.666666666666666</v>
       </c>
       <c r="BE9" s="3"/>
       <c r="BF9" s="3"/>
@@ -2561,7 +2561,7 @@
         <v>105409.9872037921</v>
       </c>
       <c r="L10" s="17">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M10" s="17"/>
       <c r="N10" s="6"/>
@@ -2587,7 +2587,7 @@
         <v>115950.98592417133</v>
       </c>
       <c r="W10" s="17">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="X10" s="17"/>
       <c r="Y10" s="17"/>
@@ -2611,7 +2611,7 @@
         <v>115950.98592417133</v>
       </c>
       <c r="AH10" s="17">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AI10" s="17"/>
       <c r="AJ10" s="17"/>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="AS10" s="17">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AT10" s="17"/>
       <c r="AU10" s="17"/>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BD10" s="3">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BE10" s="3"/>
       <c r="BF10" s="3"/>
@@ -2739,7 +2739,7 @@
         <v>92529.711095863735</v>
       </c>
       <c r="L11" s="17">
-        <v>26</v>
+        <v>8.6666666666666661</v>
       </c>
       <c r="M11" s="17"/>
       <c r="N11" s="6"/>
@@ -2765,7 +2765,7 @@
         <v>101782.68220545011</v>
       </c>
       <c r="W11" s="17">
-        <v>26</v>
+        <v>8.6666666666666661</v>
       </c>
       <c r="X11" s="17"/>
       <c r="Y11" s="17"/>
@@ -2789,7 +2789,7 @@
         <v>101782.68220545011</v>
       </c>
       <c r="AH11" s="17">
-        <v>26</v>
+        <v>8.6666666666666661</v>
       </c>
       <c r="AI11" s="17"/>
       <c r="AJ11" s="17"/>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="AS11" s="17">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>8.6666666666666661</v>
       </c>
       <c r="AT11" s="17"/>
       <c r="AU11" s="17"/>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="BD11" s="3">
         <f t="shared" si="1"/>
-        <v>26</v>
+        <v>8.6666666666666661</v>
       </c>
       <c r="BE11" s="3"/>
       <c r="BF11" s="3"/>
@@ -2917,7 +2917,7 @@
         <v>139210.95651634005</v>
       </c>
       <c r="L12" s="17">
-        <v>169.2</v>
+        <v>56.4</v>
       </c>
       <c r="M12" s="17"/>
       <c r="N12" s="6"/>
@@ -2943,7 +2943,7 @@
         <v>153132.05216797406</v>
       </c>
       <c r="W12" s="17">
-        <v>169.2</v>
+        <v>56.4</v>
       </c>
       <c r="X12" s="17"/>
       <c r="Y12" s="17"/>
@@ -2967,7 +2967,7 @@
         <v>153132.05216797406</v>
       </c>
       <c r="AH12" s="17">
-        <v>169.2</v>
+        <v>56.4</v>
       </c>
       <c r="AI12" s="17"/>
       <c r="AJ12" s="17"/>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AS12" s="17">
         <f t="shared" si="4"/>
-        <v>169.2</v>
+        <v>56.4</v>
       </c>
       <c r="AT12" s="17"/>
       <c r="AU12" s="17"/>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="BD12" s="3">
         <f t="shared" si="1"/>
-        <v>169.2</v>
+        <v>56.4</v>
       </c>
       <c r="BE12" s="3"/>
       <c r="BF12" s="3"/>
@@ -3091,7 +3091,7 @@
         <v>127874.84755439906</v>
       </c>
       <c r="L13" s="17">
-        <v>7.2</v>
+        <v>2.4</v>
       </c>
       <c r="M13" s="17"/>
       <c r="N13" s="6"/>
@@ -3117,7 +3117,7 @@
         <v>140662.332309839</v>
       </c>
       <c r="W13" s="17">
-        <v>7.2</v>
+        <v>2.4</v>
       </c>
       <c r="X13" s="17"/>
       <c r="Y13" s="17"/>
@@ -3141,7 +3141,7 @@
         <v>140662.332309839</v>
       </c>
       <c r="AH13" s="17">
-        <v>7.2</v>
+        <v>2.4</v>
       </c>
       <c r="AI13" s="17"/>
       <c r="AJ13" s="17"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="AS13" s="17">
         <f t="shared" si="4"/>
-        <v>7.2</v>
+        <v>2.4</v>
       </c>
       <c r="AT13" s="17"/>
       <c r="AU13" s="17"/>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BD13" s="3">
         <f t="shared" si="1"/>
-        <v>7.2</v>
+        <v>2.4</v>
       </c>
       <c r="BE13" s="3"/>
       <c r="BF13" s="3"/>
@@ -3266,7 +3266,7 @@
         <v>90000</v>
       </c>
       <c r="L14" s="17">
-        <v>4.05</v>
+        <v>1.3499999999999999</v>
       </c>
       <c r="M14" s="17"/>
       <c r="N14" s="6"/>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="BD14" s="3">
         <f t="shared" si="1"/>
-        <v>1.0125</v>
+        <v>0.33749999999999997</v>
       </c>
       <c r="BE14" s="3"/>
       <c r="BF14" s="3"/>
@@ -3616,7 +3616,7 @@
         <v>84493.658345803764</v>
       </c>
       <c r="L16" s="17">
-        <v>11</v>
+        <v>3.6666666666666665</v>
       </c>
       <c r="M16" s="17"/>
       <c r="N16" s="6"/>
@@ -3642,7 +3642,7 @@
         <v>92943.024180384149</v>
       </c>
       <c r="W16" s="17">
-        <v>11</v>
+        <v>3.6666666666666665</v>
       </c>
       <c r="X16" s="17"/>
       <c r="Y16" s="17"/>
@@ -3666,7 +3666,7 @@
         <v>92943.024180384149</v>
       </c>
       <c r="AH16" s="17">
-        <v>11</v>
+        <v>3.6666666666666665</v>
       </c>
       <c r="AI16" s="17"/>
       <c r="AJ16" s="17"/>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AS16" s="17">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>3.6666666666666665</v>
       </c>
       <c r="AT16" s="17"/>
       <c r="AU16" s="17"/>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="BD16" s="3">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>3.6666666666666665</v>
       </c>
       <c r="BE16" s="3"/>
       <c r="BF16" s="3"/>
@@ -3793,7 +3793,7 @@
         <v>93889.935253165968</v>
       </c>
       <c r="L17" s="17">
-        <v>242</v>
+        <v>80.666666666666671</v>
       </c>
       <c r="M17" s="17"/>
       <c r="N17" s="6"/>
@@ -3819,7 +3819,7 @@
         <v>103278.92877848257</v>
       </c>
       <c r="W17" s="17">
-        <v>242</v>
+        <v>80.666666666666671</v>
       </c>
       <c r="X17" s="17"/>
       <c r="Y17" s="17"/>
@@ -3843,7 +3843,7 @@
         <v>103278.92877848257</v>
       </c>
       <c r="AH17" s="17">
-        <v>242</v>
+        <v>80.666666666666671</v>
       </c>
       <c r="AI17" s="17"/>
       <c r="AJ17" s="17"/>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="AS17" s="17">
         <f t="shared" si="4"/>
-        <v>242</v>
+        <v>80.666666666666671</v>
       </c>
       <c r="AT17" s="17"/>
       <c r="AU17" s="17"/>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="BD17" s="3">
         <f t="shared" si="1"/>
-        <v>242</v>
+        <v>80.666666666666671</v>
       </c>
       <c r="BE17" s="3"/>
       <c r="BF17" s="3"/>
@@ -3971,7 +3971,7 @@
         <v>130642.86165864758</v>
       </c>
       <c r="L18" s="17">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M18" s="17"/>
       <c r="N18" s="6"/>
@@ -3997,7 +3997,7 @@
         <v>143707.14782451236</v>
       </c>
       <c r="W18" s="17">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="X18" s="17"/>
       <c r="Y18" s="17"/>
@@ -4021,7 +4021,7 @@
         <v>143707.14782451236</v>
       </c>
       <c r="AH18" s="17">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AI18" s="17"/>
       <c r="AJ18" s="17"/>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="AS18" s="17">
         <f t="shared" si="4"/>
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AT18" s="17"/>
       <c r="AU18" s="17"/>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="BD18" s="3">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="BE18" s="3"/>
       <c r="BF18" s="3"/>
@@ -4143,7 +4143,7 @@
         <v>98824.569981892113</v>
       </c>
       <c r="L19" s="17">
-        <v>36.599999999999994</v>
+        <v>12.199999999999998</v>
       </c>
       <c r="M19" s="17"/>
       <c r="N19" s="6"/>
@@ -4169,7 +4169,7 @@
         <v>108707.02698008134</v>
       </c>
       <c r="W19" s="17">
-        <v>36.599999999999994</v>
+        <v>12.199999999999998</v>
       </c>
       <c r="X19" s="17"/>
       <c r="Y19" s="17"/>
@@ -4193,7 +4193,7 @@
         <v>108707.02698008134</v>
       </c>
       <c r="AH19" s="17">
-        <v>36.599999999999994</v>
+        <v>12.199999999999998</v>
       </c>
       <c r="AI19" s="17"/>
       <c r="AJ19" s="17"/>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="AS19" s="17">
         <f t="shared" si="4"/>
-        <v>36.599999999999994</v>
+        <v>12.199999999999998</v>
       </c>
       <c r="AT19" s="17"/>
       <c r="AU19" s="17"/>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="BD19" s="3">
         <f t="shared" si="1"/>
-        <v>36.599999999999994</v>
+        <v>12.199999999999998</v>
       </c>
       <c r="BE19" s="3"/>
       <c r="BF19" s="3"/>
@@ -4318,7 +4318,7 @@
         <v>87648.628603046702</v>
       </c>
       <c r="L20" s="17">
-        <v>13</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="M20" s="17"/>
       <c r="N20" s="6"/>
@@ -4344,7 +4344,7 @@
         <v>96413.491463351384</v>
       </c>
       <c r="W20" s="17">
-        <v>13</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="X20" s="17"/>
       <c r="Y20" s="17"/>
@@ -4368,7 +4368,7 @@
         <v>96413.491463351384</v>
       </c>
       <c r="AH20" s="17">
-        <v>13</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="AI20" s="17"/>
       <c r="AJ20" s="17"/>
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AS20" s="17">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="AT20" s="17"/>
       <c r="AU20" s="17"/>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="BD20" s="3">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="BE20" s="3"/>
       <c r="BF20" s="3"/>
@@ -4497,7 +4497,7 @@
         <v>92605.584307238096</v>
       </c>
       <c r="L21" s="17">
-        <v>106.5</v>
+        <v>35.5</v>
       </c>
       <c r="M21" s="17"/>
       <c r="N21" s="6"/>
@@ -4523,7 +4523,7 @@
         <v>101866.14273796191</v>
       </c>
       <c r="W21" s="17">
-        <v>106.5</v>
+        <v>35.5</v>
       </c>
       <c r="X21" s="17"/>
       <c r="Y21" s="17"/>
@@ -4547,7 +4547,7 @@
         <v>101866.14273796191</v>
       </c>
       <c r="AH21" s="17">
-        <v>106.5</v>
+        <v>35.5</v>
       </c>
       <c r="AI21" s="17"/>
       <c r="AJ21" s="17"/>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="AS21" s="17">
         <f t="shared" si="4"/>
-        <v>106.5</v>
+        <v>35.5</v>
       </c>
       <c r="AT21" s="17"/>
       <c r="AU21" s="17"/>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="BD21" s="3">
         <f t="shared" si="1"/>
-        <v>106.5</v>
+        <v>35.5</v>
       </c>
       <c r="BE21" s="3"/>
       <c r="BF21" s="3"/>
@@ -4675,7 +4675,7 @@
         <v>103085.48499783476</v>
       </c>
       <c r="L22" s="17">
-        <v>2</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="M22" s="17"/>
       <c r="N22" s="6"/>
@@ -4701,7 +4701,7 @@
         <v>113394.03349761825</v>
       </c>
       <c r="W22" s="17">
-        <v>2</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="X22" s="17"/>
       <c r="Y22" s="17"/>
@@ -4725,7 +4725,7 @@
         <v>113394.03349761825</v>
       </c>
       <c r="AH22" s="17">
-        <v>2</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AI22" s="17"/>
       <c r="AJ22" s="17"/>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="AS22" s="17">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AT22" s="17"/>
       <c r="AU22" s="17"/>
@@ -4780,7 +4780,7 @@
       </c>
       <c r="BD22" s="3">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BE22" s="3"/>
       <c r="BF22" s="3"/>
@@ -4849,7 +4849,7 @@
         <v>110145.72220882092</v>
       </c>
       <c r="L23" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M23" s="17"/>
       <c r="N23" s="6"/>
@@ -4875,7 +4875,7 @@
         <v>121160.29442970302</v>
       </c>
       <c r="W23" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X23" s="17"/>
       <c r="Y23" s="17"/>
@@ -4899,7 +4899,7 @@
         <v>121160.29442970302</v>
       </c>
       <c r="AH23" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI23" s="17"/>
       <c r="AJ23" s="17"/>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AS23" s="17">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AT23" s="17"/>
       <c r="AU23" s="17"/>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="BD23" s="3">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BE23" s="3"/>
       <c r="BF23" s="3"/>
@@ -5029,7 +5029,7 @@
         <v>100838.35645704676</v>
       </c>
       <c r="L24" s="17">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M24" s="17"/>
       <c r="N24" s="6"/>
@@ -5055,7 +5055,7 @@
         <v>110922.19210275145</v>
       </c>
       <c r="W24" s="17">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="X24" s="17"/>
       <c r="Y24" s="17"/>
@@ -5079,7 +5079,7 @@
         <v>110922.19210275145</v>
       </c>
       <c r="AH24" s="17">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AI24" s="17"/>
       <c r="AJ24" s="17"/>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="AS24" s="17">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AT24" s="17"/>
       <c r="AU24" s="17"/>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="BD24" s="3">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="BE24" s="3"/>
       <c r="BF24" s="3"/>
@@ -5207,7 +5207,7 @@
         <v>99879.714553386511</v>
       </c>
       <c r="L25" s="17">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M25" s="17"/>
       <c r="N25" s="6"/>
@@ -5233,7 +5233,7 @@
         <v>109867.68600872517</v>
       </c>
       <c r="W25" s="17">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="X25" s="17"/>
       <c r="Y25" s="17"/>
@@ -5257,7 +5257,7 @@
         <v>109867.68600872517</v>
       </c>
       <c r="AH25" s="17">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AI25" s="17"/>
       <c r="AJ25" s="17"/>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="AS25" s="17">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AT25" s="17"/>
       <c r="AU25" s="17"/>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="BD25" s="3">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="BE25" s="3"/>
       <c r="BF25" s="3"/>
@@ -5385,7 +5385,7 @@
         <v>117138.77421768615</v>
       </c>
       <c r="L26" s="17">
-        <v>56</v>
+        <v>18.666666666666668</v>
       </c>
       <c r="M26" s="17"/>
       <c r="N26" s="6"/>
@@ -5411,7 +5411,7 @@
         <v>128852.65163945478</v>
       </c>
       <c r="W26" s="17">
-        <v>56</v>
+        <v>18.666666666666668</v>
       </c>
       <c r="X26" s="17"/>
       <c r="Y26" s="17"/>
@@ -5435,7 +5435,7 @@
         <v>128852.65163945478</v>
       </c>
       <c r="AH26" s="17">
-        <v>56</v>
+        <v>18.666666666666668</v>
       </c>
       <c r="AI26" s="17"/>
       <c r="AJ26" s="17"/>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="AS26" s="17">
         <f t="shared" si="4"/>
-        <v>56</v>
+        <v>18.666666666666668</v>
       </c>
       <c r="AT26" s="17"/>
       <c r="AU26" s="17"/>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="BD26" s="3">
         <f t="shared" si="1"/>
-        <v>56</v>
+        <v>18.666666666666668</v>
       </c>
       <c r="BE26" s="3"/>
       <c r="BF26" s="3"/>
@@ -5562,7 +5562,7 @@
         <v>130317.5227990795</v>
       </c>
       <c r="L27" s="17">
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="M27" s="17"/>
       <c r="N27" s="6"/>
@@ -5588,7 +5588,7 @@
         <v>143349.27507898747</v>
       </c>
       <c r="W27" s="17">
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="X27" s="17"/>
       <c r="Y27" s="17"/>
@@ -5612,7 +5612,7 @@
         <v>143349.27507898747</v>
       </c>
       <c r="AH27" s="17">
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AI27" s="17"/>
       <c r="AJ27" s="17"/>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="AS27" s="17">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AT27" s="17"/>
       <c r="AU27" s="17"/>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="BD27" s="3">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="BE27" s="3"/>
       <c r="BF27" s="3"/>
@@ -5734,7 +5734,7 @@
         <v>83282.006813596032</v>
       </c>
       <c r="L28" s="17">
-        <v>40</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="M28" s="17"/>
       <c r="N28" s="6"/>
@@ -5760,7 +5760,7 @@
         <v>91610.207494955641</v>
       </c>
       <c r="W28" s="17">
-        <v>40</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="X28" s="17"/>
       <c r="Y28" s="17"/>
@@ -5784,7 +5784,7 @@
         <v>91610.207494955641</v>
       </c>
       <c r="AH28" s="17">
-        <v>40</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="AI28" s="17"/>
       <c r="AJ28" s="17"/>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="AS28" s="17">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="AT28" s="17"/>
       <c r="AU28" s="17"/>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="BD28" s="3">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="BE28" s="3"/>
       <c r="BF28" s="3"/>
@@ -5908,7 +5908,7 @@
         <v>91755.335649669636</v>
       </c>
       <c r="L29" s="17">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="M29" s="17"/>
       <c r="N29" s="6"/>
@@ -5934,7 +5934,7 @@
         <v>100930.86921463661</v>
       </c>
       <c r="W29" s="17">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="X29" s="17"/>
       <c r="Y29" s="17"/>
@@ -5958,7 +5958,7 @@
         <v>100930.86921463661</v>
       </c>
       <c r="AH29" s="17">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="AI29" s="17"/>
       <c r="AJ29" s="17"/>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="AS29" s="17">
         <f t="shared" si="4"/>
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="AT29" s="17"/>
       <c r="AU29" s="17"/>
@@ -6013,7 +6013,7 @@
       </c>
       <c r="BD29" s="3">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="BE29" s="3"/>
       <c r="BF29" s="3"/>
@@ -6259,7 +6259,7 @@
         <v>92547.060993046674</v>
       </c>
       <c r="L31" s="17">
-        <v>83</v>
+        <v>27.666666666666668</v>
       </c>
       <c r="M31" s="17"/>
       <c r="N31" s="6"/>
@@ -6285,7 +6285,7 @@
         <v>101801.76709235135</v>
       </c>
       <c r="W31" s="17">
-        <v>83</v>
+        <v>27.666666666666668</v>
       </c>
       <c r="X31" s="17"/>
       <c r="Y31" s="17"/>
@@ -6309,7 +6309,7 @@
         <v>101801.76709235135</v>
       </c>
       <c r="AH31" s="17">
-        <v>83</v>
+        <v>27.666666666666668</v>
       </c>
       <c r="AI31" s="17"/>
       <c r="AJ31" s="17"/>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AS31" s="17">
         <f t="shared" si="4"/>
-        <v>83</v>
+        <v>27.666666666666668</v>
       </c>
       <c r="AT31" s="17"/>
       <c r="AU31" s="17"/>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="BD31" s="3">
         <f t="shared" si="1"/>
-        <v>83</v>
+        <v>27.666666666666668</v>
       </c>
       <c r="BE31" s="3"/>
       <c r="BF31" s="3"/>
@@ -6434,7 +6434,7 @@
         <v>87949.115935818816</v>
       </c>
       <c r="L32" s="17">
-        <v>43</v>
+        <v>14.333333333333334</v>
       </c>
       <c r="M32" s="17"/>
       <c r="N32" s="6"/>
@@ -6460,7 +6460,7 @@
         <v>96744.027529400701</v>
       </c>
       <c r="W32" s="17">
-        <v>43</v>
+        <v>14.333333333333334</v>
       </c>
       <c r="X32" s="17"/>
       <c r="Y32" s="17"/>
@@ -6484,7 +6484,7 @@
         <v>96744.027529400701</v>
       </c>
       <c r="AH32" s="17">
-        <v>43</v>
+        <v>14.333333333333334</v>
       </c>
       <c r="AI32" s="17"/>
       <c r="AJ32" s="17"/>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="AS32" s="17">
         <f t="shared" si="4"/>
-        <v>43</v>
+        <v>14.333333333333334</v>
       </c>
       <c r="AT32" s="17"/>
       <c r="AU32" s="17"/>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="BD32" s="3">
         <f t="shared" si="1"/>
-        <v>43</v>
+        <v>14.333333333333334</v>
       </c>
       <c r="BE32" s="3"/>
       <c r="BF32" s="3"/>
@@ -6612,7 +6612,7 @@
         <v>122240.75445787013</v>
       </c>
       <c r="L33" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M33" s="17"/>
       <c r="N33" s="6"/>
@@ -6638,7 +6638,7 @@
         <v>134464.82990365717</v>
       </c>
       <c r="W33" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X33" s="17"/>
       <c r="Y33" s="17"/>
@@ -6662,7 +6662,7 @@
         <v>134464.82990365717</v>
       </c>
       <c r="AH33" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI33" s="17"/>
       <c r="AJ33" s="17"/>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="AS33" s="17">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AT33" s="17"/>
       <c r="AU33" s="17"/>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="BD33" s="3">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BE33" s="3"/>
       <c r="BF33" s="3"/>
@@ -6960,7 +6960,7 @@
         <v>95201.325533781623</v>
       </c>
       <c r="L35" s="17">
-        <v>7</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="M35" s="17"/>
       <c r="N35" s="6"/>
@@ -6986,7 +6986,7 @@
         <v>104721.45808715979</v>
       </c>
       <c r="W35" s="17">
-        <v>7</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="X35" s="17"/>
       <c r="Y35" s="17"/>
@@ -7010,7 +7010,7 @@
         <v>104721.45808715979</v>
       </c>
       <c r="AH35" s="17">
-        <v>7</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="AI35" s="17"/>
       <c r="AJ35" s="17"/>
@@ -7035,7 +7035,7 @@
       </c>
       <c r="AS35" s="17">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="AT35" s="17"/>
       <c r="AU35" s="17"/>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="BD35" s="3">
         <f t="shared" ref="BD35:BD59" si="11">AVERAGE(L35,W35,AH35,AS35)</f>
-        <v>7</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="BE35" s="3"/>
       <c r="BF35" s="3"/>
@@ -7134,7 +7134,7 @@
         <v>82348.641423246372</v>
       </c>
       <c r="L36" s="17">
-        <v>16</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="M36" s="17"/>
       <c r="N36" s="6"/>
@@ -7160,7 +7160,7 @@
         <v>90583.505565571017</v>
       </c>
       <c r="W36" s="17">
-        <v>16</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="X36" s="17"/>
       <c r="Y36" s="17"/>
@@ -7184,7 +7184,7 @@
         <v>90583.505565571017</v>
       </c>
       <c r="AH36" s="17">
-        <v>16</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="AI36" s="17"/>
       <c r="AJ36" s="17"/>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="AS36" s="17">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="AT36" s="17"/>
       <c r="AU36" s="17"/>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="BD36" s="3">
         <f t="shared" si="11"/>
-        <v>16</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="BE36" s="3"/>
       <c r="BF36" s="3"/>
@@ -7312,7 +7312,7 @@
         <v>94388.83163095171</v>
       </c>
       <c r="L37" s="17">
-        <v>122</v>
+        <v>40.666666666666664</v>
       </c>
       <c r="M37" s="17"/>
       <c r="N37" s="6"/>
@@ -7338,7 +7338,7 @@
         <v>103827.71479404689</v>
       </c>
       <c r="W37" s="17">
-        <v>122</v>
+        <v>40.666666666666664</v>
       </c>
       <c r="X37" s="17"/>
       <c r="Y37" s="17"/>
@@ -7362,7 +7362,7 @@
         <v>103827.71479404689</v>
       </c>
       <c r="AH37" s="17">
-        <v>122</v>
+        <v>40.666666666666664</v>
       </c>
       <c r="AI37" s="17"/>
       <c r="AJ37" s="17"/>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="AS37" s="17">
         <f t="shared" si="4"/>
-        <v>122</v>
+        <v>40.666666666666664</v>
       </c>
       <c r="AT37" s="17"/>
       <c r="AU37" s="17"/>
@@ -7417,7 +7417,7 @@
       </c>
       <c r="BD37" s="3">
         <f t="shared" si="11"/>
-        <v>122</v>
+        <v>40.666666666666664</v>
       </c>
       <c r="BE37" s="3"/>
       <c r="BF37" s="3"/>
@@ -7486,7 +7486,7 @@
         <v>100619.43490047885</v>
       </c>
       <c r="L38" s="17">
-        <v>35</v>
+        <v>11.666666666666666</v>
       </c>
       <c r="M38" s="17"/>
       <c r="N38" s="6"/>
@@ -7512,7 +7512,7 @@
         <v>110681.37839052675</v>
       </c>
       <c r="W38" s="17">
-        <v>35</v>
+        <v>11.666666666666666</v>
       </c>
       <c r="X38" s="17"/>
       <c r="Y38" s="17"/>
@@ -7536,7 +7536,7 @@
         <v>110681.37839052675</v>
       </c>
       <c r="AH38" s="17">
-        <v>35</v>
+        <v>11.666666666666666</v>
       </c>
       <c r="AI38" s="17"/>
       <c r="AJ38" s="17"/>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="AS38" s="17">
         <f t="shared" si="4"/>
-        <v>35</v>
+        <v>11.666666666666666</v>
       </c>
       <c r="AT38" s="17"/>
       <c r="AU38" s="17"/>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="BD38" s="3">
         <f t="shared" si="11"/>
-        <v>35</v>
+        <v>11.666666666666666</v>
       </c>
       <c r="BE38" s="3"/>
       <c r="BF38" s="3"/>
@@ -7660,7 +7660,7 @@
         <v>93473.032591125986</v>
       </c>
       <c r="L39" s="17">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M39" s="17"/>
       <c r="N39" s="6"/>
@@ -7686,7 +7686,7 @@
         <v>102820.3358502386</v>
       </c>
       <c r="W39" s="17">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="X39" s="17"/>
       <c r="Y39" s="17"/>
@@ -7710,7 +7710,7 @@
         <v>102820.3358502386</v>
       </c>
       <c r="AH39" s="17">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AI39" s="17"/>
       <c r="AJ39" s="17"/>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="AS39" s="17">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AT39" s="17"/>
       <c r="AU39" s="17"/>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="BD39" s="3">
         <f t="shared" si="11"/>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="BE39" s="3"/>
       <c r="BF39" s="3"/>
@@ -7834,7 +7834,7 @@
         <v>102889.40225520697</v>
       </c>
       <c r="L40" s="17">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M40" s="17"/>
       <c r="N40" s="6"/>
@@ -7860,7 +7860,7 @@
         <v>113178.34248072768</v>
       </c>
       <c r="W40" s="17">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="X40" s="17"/>
       <c r="Y40" s="17"/>
@@ -7884,7 +7884,7 @@
         <v>113178.34248072768</v>
       </c>
       <c r="AH40" s="17">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AI40" s="17"/>
       <c r="AJ40" s="17"/>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="AS40" s="17">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AT40" s="17"/>
       <c r="AU40" s="17"/>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="BD40" s="3">
         <f t="shared" si="11"/>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="BE40" s="3"/>
       <c r="BF40" s="3"/>
@@ -8184,7 +8184,7 @@
         <v>109174.83125485166</v>
       </c>
       <c r="L42" s="17">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M42" s="17"/>
       <c r="N42" s="6"/>
@@ -8210,7 +8210,7 @@
         <v>120092.31438033683</v>
       </c>
       <c r="W42" s="17">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="X42" s="17"/>
       <c r="Y42" s="17"/>
@@ -8234,7 +8234,7 @@
         <v>120092.31438033683</v>
       </c>
       <c r="AH42" s="17">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AI42" s="17"/>
       <c r="AJ42" s="17"/>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="AS42" s="17">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AT42" s="17"/>
       <c r="AU42" s="17"/>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="BD42" s="3">
         <f t="shared" si="11"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="BE42" s="3"/>
       <c r="BF42" s="3"/>
@@ -8362,7 +8362,7 @@
         <v>90000</v>
       </c>
       <c r="L43" s="17">
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="M43" s="17"/>
       <c r="N43" s="6"/>
@@ -8467,7 +8467,7 @@
       </c>
       <c r="BD43" s="3">
         <f t="shared" si="11"/>
-        <v>0.25</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="BE43" s="3"/>
       <c r="BF43" s="3"/>
@@ -8534,7 +8534,7 @@
         <v>112725.33024016366</v>
       </c>
       <c r="L44" s="17">
-        <v>13.8</v>
+        <v>4.6000000000000005</v>
       </c>
       <c r="M44" s="17"/>
       <c r="N44" s="6"/>
@@ -8560,7 +8560,7 @@
         <v>123997.86326418004</v>
       </c>
       <c r="W44" s="17">
-        <v>13.8</v>
+        <v>4.6000000000000005</v>
       </c>
       <c r="X44" s="17"/>
       <c r="Y44" s="17"/>
@@ -8584,7 +8584,7 @@
         <v>123997.86326418004</v>
       </c>
       <c r="AH44" s="17">
-        <v>13.8</v>
+        <v>4.6000000000000005</v>
       </c>
       <c r="AI44" s="17"/>
       <c r="AJ44" s="17"/>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="AS44" s="17">
         <f t="shared" si="4"/>
-        <v>13.8</v>
+        <v>4.6000000000000005</v>
       </c>
       <c r="AT44" s="17"/>
       <c r="AU44" s="17"/>
@@ -8639,7 +8639,7 @@
       </c>
       <c r="BD44" s="3">
         <f t="shared" si="11"/>
-        <v>13.8</v>
+        <v>4.6000000000000005</v>
       </c>
       <c r="BE44" s="3"/>
       <c r="BF44" s="3"/>
@@ -8713,7 +8713,7 @@
         <v>115651.32991422365</v>
       </c>
       <c r="L45" s="17">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M45" s="17"/>
       <c r="N45" s="6"/>
@@ -8739,7 +8739,7 @@
         <v>127216.46290564603</v>
       </c>
       <c r="W45" s="17">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="X45" s="17"/>
       <c r="Y45" s="17"/>
@@ -8763,7 +8763,7 @@
         <v>127216.46290564603</v>
       </c>
       <c r="AH45" s="17">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AI45" s="17"/>
       <c r="AJ45" s="17"/>
@@ -8788,7 +8788,7 @@
       </c>
       <c r="AS45" s="17">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AT45" s="17"/>
       <c r="AU45" s="17"/>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="BD45" s="3">
         <f t="shared" si="11"/>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="BE45" s="3"/>
       <c r="BF45" s="3"/>
@@ -8888,7 +8888,7 @@
         <v>74953.145229196627</v>
       </c>
       <c r="L46" s="17">
-        <v>19</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="M46" s="17"/>
       <c r="N46" s="6"/>
@@ -8914,7 +8914,7 @@
         <v>82448.459752116294</v>
       </c>
       <c r="W46" s="17">
-        <v>19</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="X46" s="17"/>
       <c r="Y46" s="17"/>
@@ -8938,7 +8938,7 @@
         <v>82448.459752116294</v>
       </c>
       <c r="AH46" s="17">
-        <v>19</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="AI46" s="17"/>
       <c r="AJ46" s="17"/>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="AS46" s="17">
         <f t="shared" si="4"/>
-        <v>19</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="AT46" s="17"/>
       <c r="AU46" s="17"/>
@@ -8993,7 +8993,7 @@
       </c>
       <c r="BD46" s="3">
         <f t="shared" si="11"/>
-        <v>19</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="BE46" s="3"/>
       <c r="BF46" s="3"/>
@@ -9063,7 +9063,7 @@
         <v>108677.95830910001</v>
       </c>
       <c r="L47" s="17">
-        <v>7</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="M47" s="17"/>
       <c r="N47" s="6"/>
@@ -9089,7 +9089,7 @@
         <v>119545.75414001002</v>
       </c>
       <c r="W47" s="17">
-        <v>7</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="X47" s="17"/>
       <c r="Y47" s="17"/>
@@ -9113,7 +9113,7 @@
         <v>119545.75414001002</v>
       </c>
       <c r="AH47" s="17">
-        <v>7</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="AI47" s="17"/>
       <c r="AJ47" s="17"/>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="AS47" s="17">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="AT47" s="17"/>
       <c r="AU47" s="17"/>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="BD47" s="3">
         <f t="shared" si="11"/>
-        <v>7</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="BE47" s="3"/>
       <c r="BF47" s="3"/>
@@ -9235,7 +9235,7 @@
         <v>104841.14470569149</v>
       </c>
       <c r="L48" s="17">
-        <v>74</v>
+        <v>24.666666666666668</v>
       </c>
       <c r="M48" s="17"/>
       <c r="N48" s="6"/>
@@ -9261,7 +9261,7 @@
         <v>115325.25917626065</v>
       </c>
       <c r="W48" s="17">
-        <v>74</v>
+        <v>24.666666666666668</v>
       </c>
       <c r="X48" s="17"/>
       <c r="Y48" s="17"/>
@@ -9285,7 +9285,7 @@
         <v>115325.25917626065</v>
       </c>
       <c r="AH48" s="17">
-        <v>74</v>
+        <v>24.666666666666668</v>
       </c>
       <c r="AI48" s="17"/>
       <c r="AJ48" s="17"/>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="AS48" s="17">
         <f t="shared" si="4"/>
-        <v>74</v>
+        <v>24.666666666666668</v>
       </c>
       <c r="AT48" s="17"/>
       <c r="AU48" s="17"/>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="BD48" s="3">
         <f t="shared" si="11"/>
-        <v>74</v>
+        <v>24.666666666666668</v>
       </c>
       <c r="BE48" s="3"/>
       <c r="BF48" s="3"/>
@@ -9415,7 +9415,7 @@
         <v>101000</v>
       </c>
       <c r="L49" s="17">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="M49" s="17"/>
       <c r="N49" s="6"/>
@@ -9441,7 +9441,7 @@
         <v>111100.00000000001</v>
       </c>
       <c r="W49" s="17">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="X49" s="17"/>
       <c r="Y49" s="17"/>
@@ -9465,7 +9465,7 @@
         <v>111100.00000000001</v>
       </c>
       <c r="AH49" s="17">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="AI49" s="17"/>
       <c r="AJ49" s="17"/>
@@ -9490,7 +9490,7 @@
       </c>
       <c r="AS49" s="17">
         <f t="shared" si="4"/>
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="AT49" s="17"/>
       <c r="AU49" s="17"/>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="BD49" s="3">
         <f t="shared" si="11"/>
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="BE49" s="3"/>
       <c r="BF49" s="3"/>
@@ -9592,7 +9592,7 @@
         <v>101000</v>
       </c>
       <c r="L50" s="17">
-        <v>4</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="M50" s="17"/>
       <c r="N50" s="6"/>
@@ -9618,7 +9618,7 @@
         <v>111100.00000000001</v>
       </c>
       <c r="W50" s="17">
-        <v>4</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="X50" s="17"/>
       <c r="Y50" s="17"/>
@@ -9642,7 +9642,7 @@
         <v>111100.00000000001</v>
       </c>
       <c r="AH50" s="17">
-        <v>4</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="AI50" s="17"/>
       <c r="AJ50" s="17"/>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="AS50" s="17">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="AT50" s="17"/>
       <c r="AU50" s="17"/>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="BD50" s="3">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="BE50" s="3"/>
       <c r="BF50" s="3"/>
@@ -9764,7 +9764,7 @@
         <v>105755.2061585195</v>
       </c>
       <c r="L51" s="17">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="M51" s="17"/>
       <c r="N51" s="6"/>
@@ -9790,7 +9790,7 @@
         <v>116330.72677437146</v>
       </c>
       <c r="W51" s="17">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="X51" s="17"/>
       <c r="Y51" s="17"/>
@@ -9814,7 +9814,7 @@
         <v>116330.72677437146</v>
       </c>
       <c r="AH51" s="17">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AI51" s="17"/>
       <c r="AJ51" s="17"/>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AS51" s="17">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AT51" s="17"/>
       <c r="AU51" s="17"/>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="BD51" s="3">
         <f t="shared" si="11"/>
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="BE51" s="3"/>
       <c r="BF51" s="3"/>
@@ -9936,7 +9936,7 @@
         <v>139414.16149187722</v>
       </c>
       <c r="L52" s="17">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M52" s="17"/>
       <c r="N52" s="6"/>
@@ -9962,7 +9962,7 @@
         <v>153355.57764106497</v>
       </c>
       <c r="W52" s="17">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="X52" s="17"/>
       <c r="Y52" s="17"/>
@@ -9986,7 +9986,7 @@
         <v>153355.57764106497</v>
       </c>
       <c r="AH52" s="17">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AI52" s="17"/>
       <c r="AJ52" s="17"/>
@@ -10011,7 +10011,7 @@
       </c>
       <c r="AS52" s="17">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AT52" s="17"/>
       <c r="AU52" s="17"/>
@@ -10041,7 +10041,7 @@
       </c>
       <c r="BD52" s="3">
         <f t="shared" si="11"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BE52" s="3"/>
       <c r="BF52" s="3"/>
@@ -10452,7 +10452,7 @@
         <v>50745.724005939614</v>
       </c>
       <c r="L55" s="17">
-        <v>64</v>
+        <v>21.333333333333332</v>
       </c>
       <c r="M55" s="17"/>
       <c r="N55" s="6"/>
@@ -10478,7 +10478,7 @@
         <v>55820.296406533576</v>
       </c>
       <c r="W55" s="17">
-        <v>64</v>
+        <v>21.333333333333332</v>
       </c>
       <c r="X55" s="17"/>
       <c r="Y55" s="17"/>
@@ -10502,7 +10502,7 @@
         <v>55820.296406533576</v>
       </c>
       <c r="AH55" s="17">
-        <v>64</v>
+        <v>21.333333333333332</v>
       </c>
       <c r="AI55" s="17"/>
       <c r="AJ55" s="17"/>
@@ -10527,7 +10527,7 @@
       </c>
       <c r="AS55" s="17">
         <f t="shared" si="4"/>
-        <v>64</v>
+        <v>21.333333333333332</v>
       </c>
       <c r="AT55" s="17"/>
       <c r="AU55" s="17"/>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="BD55" s="3">
         <f t="shared" si="11"/>
-        <v>64</v>
+        <v>21.333333333333332</v>
       </c>
       <c r="BE55" s="3"/>
       <c r="BF55" s="3"/>
@@ -10624,7 +10624,7 @@
         <v>101000</v>
       </c>
       <c r="L56" s="17">
-        <v>2.4</v>
+        <v>0.79999999999999993</v>
       </c>
       <c r="M56" s="17"/>
       <c r="N56" s="6"/>
@@ -10650,7 +10650,7 @@
         <v>111100.00000000001</v>
       </c>
       <c r="W56" s="17">
-        <v>2.4</v>
+        <v>0.79999999999999993</v>
       </c>
       <c r="X56" s="17"/>
       <c r="Y56" s="17"/>
@@ -10674,7 +10674,7 @@
         <v>111100.00000000001</v>
       </c>
       <c r="AH56" s="17">
-        <v>2.4</v>
+        <v>0.79999999999999993</v>
       </c>
       <c r="AI56" s="17"/>
       <c r="AJ56" s="17"/>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="AS56" s="17">
         <f t="shared" si="4"/>
-        <v>2.4</v>
+        <v>0.79999999999999993</v>
       </c>
       <c r="AT56" s="17"/>
       <c r="AU56" s="17"/>
@@ -10729,7 +10729,7 @@
       </c>
       <c r="BD56" s="3">
         <f t="shared" si="11"/>
-        <v>2.4</v>
+        <v>0.79999999999999993</v>
       </c>
       <c r="BE56" s="3"/>
       <c r="BF56" s="3"/>
@@ -10800,7 +10800,7 @@
         <v>448176.65956779307</v>
       </c>
       <c r="L57" s="17">
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="M57" s="17"/>
       <c r="N57" s="6"/>
@@ -10826,7 +10826,7 @@
         <v>492994.3255245724</v>
       </c>
       <c r="W57" s="17">
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="X57" s="17"/>
       <c r="Y57" s="17"/>
@@ -10850,7 +10850,7 @@
         <v>492994.3255245724</v>
       </c>
       <c r="AH57" s="17">
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AI57" s="17"/>
       <c r="AJ57" s="17"/>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="AS57" s="17">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AT57" s="17"/>
       <c r="AU57" s="17"/>
@@ -10905,7 +10905,7 @@
       </c>
       <c r="BD57" s="3">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="BE57" s="3"/>
       <c r="BF57" s="3"/>
@@ -10971,7 +10971,7 @@
         <v>90000</v>
       </c>
       <c r="L58" s="17">
-        <v>3.5</v>
+        <v>1.1666666666666667</v>
       </c>
       <c r="M58" s="17"/>
       <c r="N58" s="6"/>
@@ -10988,7 +10988,9 @@
         <v>0</v>
       </c>
       <c r="V58" s="3"/>
-      <c r="W58" s="17"/>
+      <c r="W58" s="17">
+        <v>0</v>
+      </c>
       <c r="X58" s="17"/>
       <c r="Y58" s="17"/>
       <c r="Z58" s="3"/>
@@ -11000,7 +11002,9 @@
       <c r="AE58" s="3"/>
       <c r="AF58" s="4"/>
       <c r="AG58" s="3"/>
-      <c r="AH58" s="17"/>
+      <c r="AH58" s="17">
+        <v>0</v>
+      </c>
       <c r="AI58" s="17"/>
       <c r="AJ58" s="17"/>
       <c r="AK58" s="3"/>
@@ -11050,7 +11054,7 @@
       </c>
       <c r="BD58" s="3">
         <f t="shared" si="11"/>
-        <v>1.75</v>
+        <v>0.29166666666666669</v>
       </c>
       <c r="BE58" s="5"/>
       <c r="BF58" s="5"/>
@@ -11116,7 +11120,7 @@
         <v>90000</v>
       </c>
       <c r="L59" s="17">
-        <v>1.7</v>
+        <v>0.56666666666666665</v>
       </c>
       <c r="M59" s="17"/>
       <c r="N59" s="6"/>
@@ -11133,7 +11137,9 @@
         <v>0</v>
       </c>
       <c r="V59" s="3"/>
-      <c r="W59" s="17"/>
+      <c r="W59" s="17">
+        <v>0</v>
+      </c>
       <c r="X59" s="17"/>
       <c r="Y59" s="17"/>
       <c r="Z59" s="3"/>
@@ -11145,7 +11151,9 @@
       <c r="AE59" s="3"/>
       <c r="AF59" s="4"/>
       <c r="AG59" s="3"/>
-      <c r="AH59" s="17"/>
+      <c r="AH59" s="17">
+        <v>0</v>
+      </c>
       <c r="AI59" s="17"/>
       <c r="AJ59" s="17"/>
       <c r="AK59" s="3"/>
@@ -11195,7 +11203,7 @@
       </c>
       <c r="BD59" s="3">
         <f t="shared" si="11"/>
-        <v>0.85</v>
+        <v>0.14166666666666666</v>
       </c>
       <c r="BE59" s="5"/>
       <c r="BF59" s="5"/>
@@ -11264,12 +11272,21 @@
       <c r="L60" s="24">
         <v>0</v>
       </c>
+      <c r="M60" s="17"/>
       <c r="R60">
         <v>575.60266666666666</v>
       </c>
+      <c r="W60">
+        <v>0</v>
+      </c>
+      <c r="X60" s="17"/>
       <c r="AC60">
         <v>742.6486666666666</v>
       </c>
+      <c r="AH60">
+        <v>0</v>
+      </c>
+      <c r="AI60" s="17"/>
       <c r="AN60">
         <v>995.74866666666662</v>
       </c>

--- a/CEO Review.xlsx
+++ b/CEO Review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peoplestronghrservices-my.sharepoint.com/personal/baljeet_singh_taggd_in/Documents/Desktop/Clude Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1455" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2B404CA-36CB-4987-9A65-7DDA74EBADA9}"/>
+  <xr:revisionPtr revIDLastSave="1459" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0136D6A5-674A-4810-8FA2-512D366206E8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
   </bookViews>
@@ -1424,7 +1424,7 @@
         <f t="shared" ref="BC3:BC34" si="0">AVERAGE(K3,V3,AG3,AR3)</f>
         <v>115691.90563750446</v>
       </c>
-      <c r="BD3" s="3">
+      <c r="BD3" s="7">
         <f t="shared" ref="BD3:BD34" si="1">AVERAGE(L3,W3,AH3,AS3)</f>
         <v>57.333333333333336</v>
       </c>
@@ -1598,7 +1598,7 @@
         <f t="shared" si="0"/>
         <v>186410.93693698212</v>
       </c>
-      <c r="BD4" s="3">
+      <c r="BD4" s="7">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -1773,7 +1773,7 @@
         <f t="shared" si="0"/>
         <v>108540.0911983424</v>
       </c>
-      <c r="BD5" s="3">
+      <c r="BD5" s="7">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -1950,7 +1950,7 @@
         <f t="shared" si="0"/>
         <v>118874.08964657965</v>
       </c>
-      <c r="BD6" s="3">
+      <c r="BD6" s="7">
         <f t="shared" si="1"/>
         <v>15.666666666666666</v>
       </c>
@@ -2132,7 +2132,7 @@
         <f t="shared" si="0"/>
         <v>108909.75601321482</v>
       </c>
-      <c r="BD7" s="3">
+      <c r="BD7" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -2310,7 +2310,7 @@
         <f t="shared" si="0"/>
         <v>108575</v>
       </c>
-      <c r="BD8" s="3">
+      <c r="BD8" s="7">
         <f t="shared" si="1"/>
         <v>8.1666666666666661</v>
       </c>
@@ -2485,7 +2485,7 @@
         <f t="shared" si="0"/>
         <v>86194.189818055005</v>
       </c>
-      <c r="BD9" s="3">
+      <c r="BD9" s="7">
         <f t="shared" si="1"/>
         <v>10.666666666666666</v>
       </c>
@@ -2664,7 +2664,7 @@
         <f t="shared" si="0"/>
         <v>113315.73624407653</v>
       </c>
-      <c r="BD10" s="3">
+      <c r="BD10" s="7">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -2842,7 +2842,7 @@
         <f t="shared" si="0"/>
         <v>99469.439428053534</v>
       </c>
-      <c r="BD11" s="3">
+      <c r="BD11" s="7">
         <f t="shared" si="1"/>
         <v>8.6666666666666661</v>
       </c>
@@ -3020,7 +3020,7 @@
         <f t="shared" si="0"/>
         <v>149651.77825506555</v>
       </c>
-      <c r="BD12" s="3">
+      <c r="BD12" s="7">
         <f t="shared" si="1"/>
         <v>56.4</v>
       </c>
@@ -3194,7 +3194,7 @@
         <f t="shared" si="0"/>
         <v>137465.46112097902</v>
       </c>
-      <c r="BD13" s="3">
+      <c r="BD13" s="7">
         <f t="shared" si="1"/>
         <v>2.4</v>
       </c>
@@ -3369,7 +3369,7 @@
         <f t="shared" si="0"/>
         <v>22500</v>
       </c>
-      <c r="BD14" s="3">
+      <c r="BD14" s="7">
         <f t="shared" si="1"/>
         <v>0.33749999999999997</v>
       </c>
@@ -3547,7 +3547,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BD15" s="3">
+      <c r="BD15" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3719,7 +3719,7 @@
         <f t="shared" si="0"/>
         <v>90830.682721739053</v>
       </c>
-      <c r="BD16" s="3">
+      <c r="BD16" s="7">
         <f t="shared" si="1"/>
         <v>3.6666666666666665</v>
       </c>
@@ -3896,7 +3896,7 @@
         <f t="shared" si="0"/>
         <v>100931.68039715342</v>
       </c>
-      <c r="BD17" s="3">
+      <c r="BD17" s="7">
         <f t="shared" si="1"/>
         <v>80.666666666666671</v>
       </c>
@@ -4074,7 +4074,7 @@
         <f t="shared" si="0"/>
         <v>140441.07628304616</v>
       </c>
-      <c r="BD18" s="3">
+      <c r="BD18" s="7">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -4246,7 +4246,7 @@
         <f t="shared" si="0"/>
         <v>106236.41273053404</v>
       </c>
-      <c r="BD19" s="3">
+      <c r="BD19" s="7">
         <f t="shared" si="1"/>
         <v>12.199999999999998</v>
       </c>
@@ -4421,7 +4421,7 @@
         <f t="shared" si="0"/>
         <v>94222.27574827522</v>
       </c>
-      <c r="BD20" s="3">
+      <c r="BD20" s="7">
         <f t="shared" si="1"/>
         <v>4.333333333333333</v>
       </c>
@@ -4600,7 +4600,7 @@
         <f t="shared" si="0"/>
         <v>99551.003130280951</v>
       </c>
-      <c r="BD21" s="3">
+      <c r="BD21" s="7">
         <f t="shared" si="1"/>
         <v>35.5</v>
       </c>
@@ -4778,7 +4778,7 @@
         <f t="shared" si="0"/>
         <v>110816.89637267237</v>
       </c>
-      <c r="BD22" s="3">
+      <c r="BD22" s="7">
         <f t="shared" si="1"/>
         <v>0.66666666666666663</v>
       </c>
@@ -4952,7 +4952,7 @@
         <f t="shared" si="0"/>
         <v>118406.65137448251</v>
       </c>
-      <c r="BD23" s="3">
+      <c r="BD23" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -5132,7 +5132,7 @@
         <f t="shared" si="0"/>
         <v>108401.23319132529</v>
       </c>
-      <c r="BD24" s="3">
+      <c r="BD24" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -5310,7 +5310,7 @@
         <f t="shared" si="0"/>
         <v>107370.69314489051</v>
       </c>
-      <c r="BD25" s="3">
+      <c r="BD25" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -5488,7 +5488,7 @@
         <f t="shared" si="0"/>
         <v>125924.18228401261</v>
       </c>
-      <c r="BD26" s="3">
+      <c r="BD26" s="7">
         <f t="shared" si="1"/>
         <v>18.666666666666668</v>
       </c>
@@ -5665,7 +5665,7 @@
         <f t="shared" si="0"/>
         <v>140091.33700901049</v>
       </c>
-      <c r="BD27" s="3">
+      <c r="BD27" s="7">
         <f t="shared" si="1"/>
         <v>0.33333333333333331</v>
       </c>
@@ -5837,7 +5837,7 @@
         <f t="shared" si="0"/>
         <v>89528.157324615735</v>
       </c>
-      <c r="BD28" s="3">
+      <c r="BD28" s="7">
         <f t="shared" si="1"/>
         <v>13.333333333333334</v>
       </c>
@@ -6011,7 +6011,7 @@
         <f t="shared" si="0"/>
         <v>98636.985823394876</v>
       </c>
-      <c r="BD29" s="3">
+      <c r="BD29" s="7">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
@@ -6190,7 +6190,7 @@
         <f t="shared" si="0"/>
         <v>127627.50000000001</v>
       </c>
-      <c r="BD30" s="3">
+      <c r="BD30" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6362,7 +6362,7 @@
         <f t="shared" si="0"/>
         <v>99488.090567525171</v>
       </c>
-      <c r="BD31" s="3">
+      <c r="BD31" s="7">
         <f t="shared" si="1"/>
         <v>27.666666666666668</v>
       </c>
@@ -6537,7 +6537,7 @@
         <f t="shared" si="0"/>
         <v>94545.29963100524</v>
       </c>
-      <c r="BD32" s="3">
+      <c r="BD32" s="7">
         <f t="shared" si="1"/>
         <v>14.333333333333334</v>
       </c>
@@ -6715,7 +6715,7 @@
         <f t="shared" si="0"/>
         <v>131408.81104221041</v>
       </c>
-      <c r="BD33" s="3">
+      <c r="BD33" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -6891,7 +6891,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BD34" s="3">
+      <c r="BD34" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7063,7 +7063,7 @@
         <f t="shared" ref="BC35:BC59" si="10">AVERAGE(K35,V35,AG35,AR35)</f>
         <v>102341.42494881524</v>
       </c>
-      <c r="BD35" s="3">
+      <c r="BD35" s="7">
         <f t="shared" ref="BD35:BD59" si="11">AVERAGE(L35,W35,AH35,AS35)</f>
         <v>2.3333333333333335</v>
       </c>
@@ -7237,7 +7237,7 @@
         <f t="shared" si="10"/>
         <v>88524.789529989852</v>
       </c>
-      <c r="BD36" s="3">
+      <c r="BD36" s="7">
         <f t="shared" si="11"/>
         <v>5.333333333333333</v>
       </c>
@@ -7415,7 +7415,7 @@
         <f t="shared" si="10"/>
         <v>101467.9940032731</v>
       </c>
-      <c r="BD37" s="3">
+      <c r="BD37" s="7">
         <f t="shared" si="11"/>
         <v>40.666666666666664</v>
       </c>
@@ -7589,7 +7589,7 @@
         <f t="shared" si="10"/>
         <v>108165.89251801478</v>
       </c>
-      <c r="BD38" s="3">
+      <c r="BD38" s="7">
         <f t="shared" si="11"/>
         <v>11.666666666666666</v>
       </c>
@@ -7763,7 +7763,7 @@
         <f t="shared" si="10"/>
         <v>100483.51003546044</v>
       </c>
-      <c r="BD39" s="3">
+      <c r="BD39" s="7">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
@@ -7937,7 +7937,7 @@
         <f t="shared" si="10"/>
         <v>110606.10742434752</v>
       </c>
-      <c r="BD40" s="3">
+      <c r="BD40" s="7">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
@@ -8115,7 +8115,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD41" s="3">
+      <c r="BD41" s="7">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -8287,7 +8287,7 @@
         <f t="shared" si="10"/>
         <v>117362.94359896555</v>
       </c>
-      <c r="BD42" s="3">
+      <c r="BD42" s="7">
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
@@ -8465,7 +8465,7 @@
         <f t="shared" si="10"/>
         <v>22500</v>
       </c>
-      <c r="BD43" s="3">
+      <c r="BD43" s="7">
         <f t="shared" si="11"/>
         <v>8.3333333333333329E-2</v>
       </c>
@@ -8637,7 +8637,7 @@
         <f t="shared" si="10"/>
         <v>121179.73000817593</v>
       </c>
-      <c r="BD44" s="3">
+      <c r="BD44" s="7">
         <f t="shared" si="11"/>
         <v>4.6000000000000005</v>
       </c>
@@ -8816,7 +8816,7 @@
         <f t="shared" si="10"/>
         <v>124325.17965779043</v>
       </c>
-      <c r="BD45" s="3">
+      <c r="BD45" s="7">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
@@ -8991,7 +8991,7 @@
         <f t="shared" si="10"/>
         <v>80574.631121386381</v>
       </c>
-      <c r="BD46" s="3">
+      <c r="BD46" s="7">
         <f t="shared" si="11"/>
         <v>6.333333333333333</v>
       </c>
@@ -9166,7 +9166,7 @@
         <f t="shared" si="10"/>
         <v>116828.80518228252</v>
       </c>
-      <c r="BD47" s="3">
+      <c r="BD47" s="7">
         <f t="shared" si="11"/>
         <v>2.3333333333333335</v>
       </c>
@@ -9338,7 +9338,7 @@
         <f t="shared" si="10"/>
         <v>112704.23055861835</v>
       </c>
-      <c r="BD48" s="3">
+      <c r="BD48" s="7">
         <f t="shared" si="11"/>
         <v>24.666666666666668</v>
       </c>
@@ -9518,7 +9518,7 @@
         <f t="shared" si="10"/>
         <v>108575</v>
       </c>
-      <c r="BD49" s="3">
+      <c r="BD49" s="7">
         <f t="shared" si="11"/>
         <v>19</v>
       </c>
@@ -9695,7 +9695,7 @@
         <f t="shared" si="10"/>
         <v>108575</v>
       </c>
-      <c r="BD50" s="3">
+      <c r="BD50" s="7">
         <f t="shared" si="11"/>
         <v>1.3333333333333333</v>
       </c>
@@ -9867,7 +9867,7 @@
         <f t="shared" si="10"/>
         <v>113686.84662040847</v>
       </c>
-      <c r="BD51" s="3">
+      <c r="BD51" s="7">
         <f t="shared" si="11"/>
         <v>6</v>
       </c>
@@ -10039,7 +10039,7 @@
         <f t="shared" si="10"/>
         <v>149870.22360376804</v>
       </c>
-      <c r="BD52" s="3">
+      <c r="BD52" s="7">
         <f t="shared" si="11"/>
         <v>2</v>
       </c>
@@ -10211,7 +10211,7 @@
         <f t="shared" si="10"/>
         <v>130703.60833512928</v>
       </c>
-      <c r="BD53" s="3">
+      <c r="BD53" s="7">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -10383,7 +10383,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD54" s="3">
+      <c r="BD54" s="7">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -10555,7 +10555,7 @@
         <f t="shared" si="10"/>
         <v>54551.65330638508</v>
       </c>
-      <c r="BD55" s="3">
+      <c r="BD55" s="7">
         <f t="shared" si="11"/>
         <v>21.333333333333332</v>
       </c>
@@ -10727,7 +10727,7 @@
         <f t="shared" si="10"/>
         <v>108575</v>
       </c>
-      <c r="BD56" s="3">
+      <c r="BD56" s="7">
         <f t="shared" si="11"/>
         <v>0.79999999999999993</v>
       </c>
@@ -10903,7 +10903,7 @@
         <f t="shared" si="10"/>
         <v>481789.90903537755</v>
       </c>
-      <c r="BD57" s="3">
+      <c r="BD57" s="7">
         <f t="shared" si="11"/>
         <v>0.33333333333333331</v>
       </c>
@@ -11052,7 +11052,7 @@
         <f t="shared" si="10"/>
         <v>94500</v>
       </c>
-      <c r="BD58" s="3">
+      <c r="BD58" s="7">
         <f t="shared" si="11"/>
         <v>0.29166666666666669</v>
       </c>
@@ -11201,7 +11201,7 @@
         <f t="shared" si="10"/>
         <v>94500</v>
       </c>
-      <c r="BD59" s="3">
+      <c r="BD59" s="7">
         <f t="shared" si="11"/>
         <v>0.14166666666666666</v>
       </c>
